--- a/base/StructureDefinition-SGPlanDefinition.xlsx
+++ b/base/StructureDefinition-SGPlanDefinition.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4040" uniqueCount="576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4040" uniqueCount="578">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.2.0</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>draft</t>
+    <t>active</t>
   </si>
   <si>
     <t>Experimental</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-04-02T12:10:23+02:00</t>
+    <t>2026-08-27T08:35:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}pdf-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}pdf-0:Name should be usable as an identifier for the module by machine processing applications such as code generation {name.matches('[A-Z]([A-Za-z0-9_]){0,254}')}shr-1:If knowledge capabilities are stated, they SHALL include shareable {extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').exists() implies extension('http://hl7.org/fhir/StructureDefinition/cqf-knowledgeCapability').where(value = 'shareable').exists()}</t>
   </si>
   <si>
     <t>Entity. Role, or Act</t>
@@ -358,7 +358,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -459,20 +459,8 @@
     <t>Defines a knowledge capability afforded by this knowledge artifact.</t>
   </si>
   <si>
-    <t>PlanDefinition.extension:artifactComment</t>
-  </si>
-  <si>
-    <t>artifactComment</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {cqf-artifactComment}
-</t>
-  </si>
-  <si>
-    <t>Additional documentation, review, or usage guidance</t>
-  </si>
-  <si>
-    <t>A comment containing additional documentation, a review comment, usage guidance, or other relevant information from a particular user.</t>
+    <t>ele-1
+shr-1</t>
   </si>
   <si>
     <t>PlanDefinition.extension:versionAlgorithm</t>
@@ -494,6 +482,10 @@
     <t>If set as a string, this is a FHIRPath expression that has two additional context variables passed in - %version1 and %version2 and will return a negative number if version1 is newer, a positive number if version2 and a 0 if the version ordering can't be successfully be determined.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>PlanDefinition.extension:versionPolicy</t>
   </si>
   <si>
@@ -508,6 +500,22 @@
   </si>
   <si>
     <t>Defines the versioning policy of the artifact.</t>
+  </si>
+  <si>
+    <t>PlanDefinition.extension:webSource</t>
+  </si>
+  <si>
+    <t>webSource</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {web-source}
+</t>
+  </si>
+  <si>
+    <t>web-source</t>
+  </si>
+  <si>
+    <t>Where a human readable web page describing the resource can be found, if it's at a different location to the canonical URL itself.</t>
   </si>
   <si>
     <t>PlanDefinition.modifierExtension</t>
@@ -665,7 +673,7 @@
     <t>The type of PlanDefinition.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/plan-definition-type</t>
+    <t>http://hl7.org/fhir/ValueSet/plan-definition-type|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.status</t>
@@ -721,7 +729,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(Group)</t>
+Reference(Group|4.0.1)</t>
   </si>
   <si>
     <t>Type of individual the plan definition is focused on</t>
@@ -736,7 +744,7 @@
     <t>The possible types of subjects for a plan definition (E.g. Patient, Practitioner, Organization, Location, etc.).</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/subject-type</t>
+    <t>http://hl7.org/fhir/ValueSet/subject-type|4.0.1</t>
   </si>
   <si>
     <t>Definition.subject</t>
@@ -864,7 +872,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -993,7 +1001,7 @@
     <t>High-level categorization of the definition, used for searching, sorting, and filtering.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/definition-topic</t>
+    <t>http://hl7.org/fhir/ValueSet/definition-topic|4.0.1</t>
   </si>
   <si>
     <t>Definition.subject[x]</t>
@@ -1063,7 +1071,7 @@
     <t>PlanDefinition.library</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Library)
+    <t xml:space="preserve">canonical(Library|4.0.1)
 </t>
   </si>
   <si>
@@ -1145,7 +1153,7 @@
     <t>Example codes for grouping goals for filtering or presentation.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-category</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-category|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.description</t>
@@ -1163,7 +1171,7 @@
     <t>Describes goals that can be achieved.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/clinical-findings</t>
+    <t>http://hl7.org/fhir/ValueSet/clinical-findings|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.priority</t>
@@ -1178,7 +1186,7 @@
     <t>Indicates the level of importance associated with reaching or sustaining a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-priority</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-priority|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.start</t>
@@ -1193,7 +1201,7 @@
     <t>Identifies the types of events that might trigger the start of a goal.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/goal-start-event</t>
+    <t>http://hl7.org/fhir/ValueSet/goal-start-event|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.addresses</t>
@@ -1208,7 +1216,7 @@
     <t>Identifies problems, conditions, issues, or concerns that goals may address.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/condition-code</t>
+    <t>http://hl7.org/fhir/ValueSet/condition-code|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.documentation</t>
@@ -1250,7 +1258,7 @@
     <t>Identifies types of parameters that can be tracked to determine goal achievement.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.goal.target.detail[x]</t>
@@ -1615,7 +1623,7 @@
     <t>Defines roles played by participants for the action.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-participant-role</t>
+    <t>http://hl7.org/fhir/ValueSet/action-participant-role|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.action.type</t>
@@ -1630,7 +1638,7 @@
     <t>The type of action to be performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/action-type</t>
+    <t>http://hl7.org/fhir/ValueSet/action-type|4.0.1</t>
   </si>
   <si>
     <t>PlanDefinition.action.groupingBehavior</t>
@@ -1711,7 +1719,7 @@
     <t>PlanDefinition.action.definition[x]</t>
   </si>
   <si>
-    <t>canonical(ActivityDefinition|PlanDefinition|Questionnaire)
+    <t>canonical(ActivityDefinition|4.0.1|PlanDefinition|4.0.1|Questionnaire|4.0.1)
 uri</t>
   </si>
   <si>
@@ -1730,7 +1738,7 @@
     <t>PlanDefinition.action.transform</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(StructureMap)
+    <t xml:space="preserve">canonical(StructureMap|4.0.1)
 </t>
   </si>
   <si>
@@ -2114,17 +2122,17 @@
   <dimension ref="A1:AN112"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="49.86328125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="49.86328125" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="19.65234375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="38.81640625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="5.90234375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.69921875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.07421875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="14.625" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="11.98828125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="43.58984375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="43.58984375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="17.2890625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="53.78515625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="59.7578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -2133,26 +2141,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="8.84375" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="15.71484375" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="16.08984375" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="17.078125" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="16.3125" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="95.45703125" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="56.5625" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="5.69140625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="19.73046875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="17.8203125" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="14.98828125" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="12.3046875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="43.76171875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="9.5" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="9.87890625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="84.578125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.17578125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="17.65625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="38.00390625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="86.95703125" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="38.08984375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="32.84375" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="43.078125" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="77.578125" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="34.04296875" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="41.19921875" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3181,7 +3189,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" hidden="true">
+    <row r="10">
       <c r="A10" t="s" s="2">
         <v>137</v>
       </c>
@@ -3277,7 +3285,7 @@
         <v>82</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>136</v>
@@ -3295,15 +3303,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" hidden="true">
+    <row r="11">
       <c r="A11" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B11" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C11" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D11" t="s" s="2">
         <v>20</v>
@@ -3313,7 +3321,7 @@
         <v>81</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>86</v>
@@ -3325,15 +3333,17 @@
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>146</v>
-      </c>
-      <c r="N11" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N11" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="O11" s="2"/>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -3391,7 +3401,7 @@
         <v>82</v>
       </c>
       <c r="AI11" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ11" t="s" s="2">
         <v>136</v>
@@ -3411,13 +3421,13 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C12" t="s" s="2">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="D12" t="s" s="2">
         <v>20</v>
@@ -3430,7 +3440,7 @@
         <v>77</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>86</v>
+        <v>20</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -3439,17 +3449,15 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>151</v>
-      </c>
-      <c r="N12" t="s" s="2">
-        <v>152</v>
-      </c>
+        <v>154</v>
+      </c>
+      <c r="N12" s="2"/>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
         <v>20</v>
@@ -3507,7 +3515,7 @@
         <v>82</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>136</v>
@@ -3525,15 +3533,15 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>129</v>
       </c>
       <c r="C13" t="s" s="2">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D13" t="s" s="2">
         <v>20</v>
@@ -3555,13 +3563,13 @@
         <v>20</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -3621,7 +3629,7 @@
         <v>82</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>20</v>
+        <v>149</v>
       </c>
       <c r="AJ13" t="s" s="2">
         <v>136</v>
@@ -3641,14 +3649,14 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3670,16 +3678,16 @@
         <v>130</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -3728,7 +3736,7 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>81</v>
@@ -3755,12 +3763,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3786,16 +3794,16 @@
         <v>99</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>20</v>
@@ -3844,7 +3852,7 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>81</v>
@@ -3862,10 +3870,10 @@
         <v>20</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AN15" t="s" s="2">
         <v>20</v>
@@ -3873,10 +3881,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3899,19 +3907,19 @@
         <v>86</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>20</v>
@@ -3960,7 +3968,7 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>81</v>
@@ -3978,21 +3986,21 @@
         <v>20</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
-    <row r="17" hidden="true">
+    <row r="17">
       <c r="A17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -4015,16 +4023,16 @@
         <v>86</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
@@ -4074,7 +4082,7 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>81</v>
@@ -4092,21 +4100,21 @@
         <v>20</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="AN17" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="18" hidden="true">
+    <row r="18">
       <c r="A18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -4129,19 +4137,19 @@
         <v>86</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O18" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>20</v>
@@ -4190,7 +4198,7 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>81</v>
@@ -4199,7 +4207,7 @@
         <v>77</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>97</v>
@@ -4217,12 +4225,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4245,16 +4253,16 @@
         <v>86</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -4304,7 +4312,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>81</v>
@@ -4322,7 +4330,7 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -4333,10 +4341,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4359,13 +4367,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -4416,7 +4424,7 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>81</v>
@@ -4445,10 +4453,10 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4471,13 +4479,13 @@
         <v>86</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -4504,13 +4512,13 @@
         <v>20</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>20</v>
@@ -4528,7 +4536,7 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>81</v>
@@ -4555,12 +4563,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" hidden="true">
+    <row r="22">
       <c r="A22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4586,13 +4594,13 @@
         <v>105</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
@@ -4618,13 +4626,13 @@
         <v>20</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>20</v>
@@ -4642,7 +4650,7 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>77</v>
@@ -4660,21 +4668,21 @@
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="AN22" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4697,19 +4705,19 @@
         <v>86</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="O23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>20</v>
@@ -4758,7 +4766,7 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>81</v>
@@ -4776,10 +4784,10 @@
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>20</v>
@@ -4787,10 +4795,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4813,13 +4821,13 @@
         <v>20</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -4827,7 +4835,7 @@
         <v>20</v>
       </c>
       <c r="Q24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="R24" t="s" s="2">
         <v>20</v>
@@ -4848,13 +4856,13 @@
         <v>20</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>20</v>
@@ -4872,7 +4880,7 @@
         <v>20</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>81</v>
@@ -4890,7 +4898,7 @@
         <v>20</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>20</v>
@@ -4901,14 +4909,14 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
@@ -4927,16 +4935,16 @@
         <v>86</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4986,7 +4994,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>81</v>
@@ -5004,21 +5012,21 @@
         <v>20</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>20</v>
       </c>
     </row>
-    <row r="26" hidden="true">
+    <row r="26">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5041,19 +5049,19 @@
         <v>86</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5102,7 +5110,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>81</v>
@@ -5120,10 +5128,10 @@
         <v>20</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AN26" t="s" s="2">
         <v>20</v>
@@ -5131,10 +5139,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5157,16 +5165,16 @@
         <v>86</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5216,7 +5224,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>81</v>
@@ -5234,7 +5242,7 @@
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -5243,12 +5251,12 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" hidden="true">
+    <row r="28">
       <c r="A28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5271,16 +5279,16 @@
         <v>86</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
@@ -5330,7 +5338,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>81</v>
@@ -5348,7 +5356,7 @@
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
@@ -5359,10 +5367,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5385,19 +5393,19 @@
         <v>86</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5446,7 +5454,7 @@
         <v>20</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>81</v>
@@ -5464,7 +5472,7 @@
         <v>20</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>20</v>
@@ -5475,10 +5483,10 @@
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5501,16 +5509,16 @@
         <v>86</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="O30" s="2"/>
       <c r="P30" t="s" s="2">
@@ -5536,13 +5544,13 @@
         <v>20</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>20</v>
@@ -5560,7 +5568,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>81</v>
@@ -5578,7 +5586,7 @@
         <v>20</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>20</v>
@@ -5589,10 +5597,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5615,16 +5623,16 @@
         <v>20</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5674,7 +5682,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>81</v>
@@ -5692,21 +5700,21 @@
         <v>20</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5729,13 +5737,13 @@
         <v>20</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -5786,7 +5794,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>81</v>
@@ -5815,14 +5823,14 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E33" s="2"/>
       <c r="F33" t="s" s="2">
@@ -5841,17 +5849,17 @@
         <v>20</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5900,7 +5908,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>81</v>
@@ -5918,21 +5926,21 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5955,16 +5963,16 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6014,7 +6022,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>81</v>
@@ -6032,21 +6040,21 @@
         <v>20</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6069,19 +6077,19 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6130,7 +6138,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>81</v>
@@ -6148,21 +6156,21 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6185,19 +6193,19 @@
         <v>86</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6246,7 +6254,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>81</v>
@@ -6264,21 +6272,21 @@
         <v>20</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6301,17 +6309,17 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>20</v>
@@ -6336,13 +6344,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6360,7 +6368,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>81</v>
@@ -6378,7 +6386,7 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>20</v>
@@ -6389,10 +6397,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6415,13 +6423,13 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" s="2"/>
@@ -6472,7 +6480,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>81</v>
@@ -6487,7 +6495,7 @@
         <v>97</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AL38" t="s" s="2">
         <v>20</v>
@@ -6501,10 +6509,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6527,13 +6535,13 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" s="2"/>
@@ -6584,7 +6592,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>81</v>
@@ -6613,10 +6621,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6639,13 +6647,13 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="N40" s="2"/>
       <c r="O40" s="2"/>
@@ -6696,7 +6704,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>81</v>
@@ -6711,7 +6719,7 @@
         <v>97</v>
       </c>
       <c r="AK40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AL40" t="s" s="2">
         <v>20</v>
@@ -6725,10 +6733,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6751,13 +6759,13 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="N41" s="2"/>
       <c r="O41" s="2"/>
@@ -6808,7 +6816,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>81</v>
@@ -6823,7 +6831,7 @@
         <v>97</v>
       </c>
       <c r="AK41" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AL41" t="s" s="2">
         <v>20</v>
@@ -6837,10 +6845,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6863,19 +6871,19 @@
         <v>20</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O42" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>20</v>
@@ -6924,7 +6932,7 @@
         <v>20</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>81</v>
@@ -6953,10 +6961,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6979,13 +6987,13 @@
         <v>20</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="N43" s="2"/>
       <c r="O43" s="2"/>
@@ -7036,7 +7044,7 @@
         <v>20</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>81</v>
@@ -7065,10 +7073,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7091,17 +7099,17 @@
         <v>20</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="N44" s="2"/>
       <c r="O44" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>20</v>
@@ -7150,7 +7158,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>81</v>
@@ -7179,10 +7187,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7205,13 +7213,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7262,7 +7270,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>81</v>
@@ -7277,7 +7285,7 @@
         <v>20</v>
       </c>
       <c r="AK45" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL45" t="s" s="2">
         <v>20</v>
@@ -7291,14 +7299,14 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E46" s="2"/>
       <c r="F46" t="s" s="2">
@@ -7320,13 +7328,13 @@
         <v>130</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O46" s="2"/>
       <c r="P46" t="s" s="2">
@@ -7376,7 +7384,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>81</v>
@@ -7391,7 +7399,7 @@
         <v>136</v>
       </c>
       <c r="AK46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL46" t="s" s="2">
         <v>20</v>
@@ -7405,14 +7413,14 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -7434,16 +7442,16 @@
         <v>130</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7492,7 +7500,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>81</v>
@@ -7521,10 +7529,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7547,13 +7555,13 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="N48" s="2"/>
       <c r="O48" s="2"/>
@@ -7580,13 +7588,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7604,7 +7612,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>81</v>
@@ -7633,10 +7641,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7659,16 +7667,16 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7694,13 +7702,13 @@
         <v>20</v>
       </c>
       <c r="X49" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Y49" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="Z49" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="AA49" t="s" s="2">
         <v>20</v>
@@ -7718,7 +7726,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>77</v>
@@ -7747,10 +7755,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7773,13 +7781,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7809,10 +7817,10 @@
         <v>109</v>
       </c>
       <c r="Y50" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="Z50" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="AA50" t="s" s="2">
         <v>20</v>
@@ -7830,7 +7838,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>81</v>
@@ -7859,10 +7867,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7885,13 +7893,13 @@
         <v>20</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" s="2"/>
@@ -7918,13 +7926,13 @@
         <v>20</v>
       </c>
       <c r="X51" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Y51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="Z51" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AA51" t="s" s="2">
         <v>20</v>
@@ -7942,7 +7950,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>81</v>
@@ -7971,10 +7979,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7997,13 +8005,13 @@
         <v>20</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="N52" s="2"/>
       <c r="O52" s="2"/>
@@ -8030,13 +8038,13 @@
         <v>20</v>
       </c>
       <c r="X52" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Y52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="Z52" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>20</v>
@@ -8054,7 +8062,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>81</v>
@@ -8083,10 +8091,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8109,13 +8117,13 @@
         <v>20</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8166,7 +8174,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>81</v>
@@ -8195,10 +8203,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8221,13 +8229,13 @@
         <v>20</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8278,7 +8286,7 @@
         <v>20</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>81</v>
@@ -8307,10 +8315,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8333,13 +8341,13 @@
         <v>20</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" s="2"/>
@@ -8390,7 +8398,7 @@
         <v>20</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>81</v>
@@ -8405,7 +8413,7 @@
         <v>20</v>
       </c>
       <c r="AK55" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL55" t="s" s="2">
         <v>20</v>
@@ -8419,14 +8427,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8448,13 +8456,13 @@
         <v>130</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8504,7 +8512,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>81</v>
@@ -8519,7 +8527,7 @@
         <v>136</v>
       </c>
       <c r="AK56" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL56" t="s" s="2">
         <v>20</v>
@@ -8533,14 +8541,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8562,16 +8570,16 @@
         <v>130</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>20</v>
@@ -8620,7 +8628,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>81</v>
@@ -8649,10 +8657,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8675,13 +8683,13 @@
         <v>20</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8708,13 +8716,13 @@
         <v>20</v>
       </c>
       <c r="X58" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Y58" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="Z58" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="AA58" t="s" s="2">
         <v>20</v>
@@ -8732,7 +8740,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>81</v>
@@ -8761,10 +8769,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8787,13 +8795,13 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8844,7 +8852,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>81</v>
@@ -8873,10 +8881,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8899,13 +8907,13 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8956,7 +8964,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>81</v>
@@ -8985,10 +8993,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9011,16 +9019,16 @@
         <v>20</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9070,7 +9078,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>81</v>
@@ -9088,7 +9096,7 @@
         <v>20</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>20</v>
@@ -9099,10 +9107,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9125,13 +9133,13 @@
         <v>20</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -9182,7 +9190,7 @@
         <v>20</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>81</v>
@@ -9197,7 +9205,7 @@
         <v>20</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL62" t="s" s="2">
         <v>20</v>
@@ -9211,14 +9219,14 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -9240,13 +9248,13 @@
         <v>130</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9296,7 +9304,7 @@
         <v>20</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>81</v>
@@ -9311,7 +9319,7 @@
         <v>136</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL63" t="s" s="2">
         <v>20</v>
@@ -9325,14 +9333,14 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E64" s="2"/>
       <c r="F64" t="s" s="2">
@@ -9354,16 +9362,16 @@
         <v>130</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>20</v>
@@ -9412,7 +9420,7 @@
         <v>20</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>81</v>
@@ -9441,10 +9449,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9467,13 +9475,13 @@
         <v>20</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9524,7 +9532,7 @@
         <v>20</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>81</v>
@@ -9553,10 +9561,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9579,13 +9587,13 @@
         <v>20</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9636,7 +9644,7 @@
         <v>20</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>81</v>
@@ -9654,7 +9662,7 @@
         <v>20</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>20</v>
@@ -9665,10 +9673,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9691,13 +9699,13 @@
         <v>20</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" s="2"/>
@@ -9748,7 +9756,7 @@
         <v>20</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>81</v>
@@ -9766,7 +9774,7 @@
         <v>20</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>20</v>
@@ -9777,10 +9785,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9803,13 +9811,13 @@
         <v>20</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -9860,7 +9868,7 @@
         <v>20</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>81</v>
@@ -9878,7 +9886,7 @@
         <v>20</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>20</v>
@@ -9889,10 +9897,10 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9918,10 +9926,10 @@
         <v>105</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9948,13 +9956,13 @@
         <v>20</v>
       </c>
       <c r="X69" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y69" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="Z69" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>20</v>
@@ -9972,7 +9980,7 @@
         <v>20</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>81</v>
@@ -10001,10 +10009,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10027,13 +10035,13 @@
         <v>20</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10084,7 +10092,7 @@
         <v>20</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>81</v>
@@ -10113,10 +10121,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10139,16 +10147,16 @@
         <v>20</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="O71" s="2"/>
       <c r="P71" t="s" s="2">
@@ -10198,7 +10206,7 @@
         <v>20</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>81</v>
@@ -10227,10 +10235,10 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10253,13 +10261,13 @@
         <v>20</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -10310,7 +10318,7 @@
         <v>20</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>81</v>
@@ -10339,10 +10347,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10368,10 +10376,10 @@
         <v>87</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" s="2"/>
@@ -10422,7 +10430,7 @@
         <v>20</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>81</v>
@@ -10451,10 +10459,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10477,70 +10485,70 @@
         <v>20</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M74" t="s" s="2">
+        <v>448</v>
+      </c>
+      <c r="N74" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="O74" t="s" s="2">
+        <v>450</v>
+      </c>
+      <c r="P74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="Q74" t="s" s="2">
+        <v>230</v>
+      </c>
+      <c r="R74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="S74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="T74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="U74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="V74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="W74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="X74" t="s" s="2">
+        <v>207</v>
+      </c>
+      <c r="Y74" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="Z74" t="s" s="2">
+        <v>232</v>
+      </c>
+      <c r="AA74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AB74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AC74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AD74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AE74" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="AF74" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="N74" t="s" s="2">
-        <v>447</v>
-      </c>
-      <c r="O74" t="s" s="2">
-        <v>448</v>
-      </c>
-      <c r="P74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="Q74" t="s" s="2">
-        <v>228</v>
-      </c>
-      <c r="R74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="S74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="T74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="U74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="V74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="W74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="X74" t="s" s="2">
-        <v>205</v>
-      </c>
-      <c r="Y74" t="s" s="2">
-        <v>229</v>
-      </c>
-      <c r="Z74" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="AA74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AB74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AC74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AD74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AE74" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="AF74" t="s" s="2">
-        <v>444</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>81</v>
@@ -10558,7 +10566,7 @@
         <v>20</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>20</v>
@@ -10569,10 +10577,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10595,13 +10603,13 @@
         <v>20</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -10652,7 +10660,7 @@
         <v>20</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>81</v>
@@ -10681,10 +10689,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10707,16 +10715,16 @@
         <v>20</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="O76" s="2"/>
       <c r="P76" t="s" s="2">
@@ -10766,7 +10774,7 @@
         <v>20</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>81</v>
@@ -10795,10 +10803,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10821,13 +10829,13 @@
         <v>20</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -10878,7 +10886,7 @@
         <v>20</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>81</v>
@@ -10893,7 +10901,7 @@
         <v>20</v>
       </c>
       <c r="AK77" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL77" t="s" s="2">
         <v>20</v>
@@ -10907,14 +10915,14 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E78" s="2"/>
       <c r="F78" t="s" s="2">
@@ -10936,13 +10944,13 @@
         <v>130</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N78" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O78" s="2"/>
       <c r="P78" t="s" s="2">
@@ -10992,7 +11000,7 @@
         <v>20</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>81</v>
@@ -11007,7 +11015,7 @@
         <v>136</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>20</v>
@@ -11021,14 +11029,14 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E79" s="2"/>
       <c r="F79" t="s" s="2">
@@ -11050,16 +11058,16 @@
         <v>130</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N79" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O79" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>20</v>
@@ -11108,7 +11116,7 @@
         <v>20</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>81</v>
@@ -11137,10 +11145,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11166,13 +11174,13 @@
         <v>105</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11198,13 +11206,13 @@
         <v>20</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>20</v>
@@ -11222,7 +11230,7 @@
         <v>20</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>77</v>
@@ -11251,10 +11259,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11277,16 +11285,16 @@
         <v>20</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O81" s="2"/>
       <c r="P81" t="s" s="2">
@@ -11336,7 +11344,7 @@
         <v>20</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>81</v>
@@ -11365,10 +11373,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11391,13 +11399,13 @@
         <v>20</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" s="2"/>
@@ -11448,7 +11456,7 @@
         <v>20</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>81</v>
@@ -11477,10 +11485,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11503,13 +11511,13 @@
         <v>20</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11560,7 +11568,7 @@
         <v>20</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>81</v>
@@ -11589,10 +11597,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11615,16 +11623,16 @@
         <v>20</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11674,7 +11682,7 @@
         <v>20</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>81</v>
@@ -11703,10 +11711,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11729,13 +11737,13 @@
         <v>20</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11786,7 +11794,7 @@
         <v>20</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>81</v>
@@ -11801,7 +11809,7 @@
         <v>20</v>
       </c>
       <c r="AK85" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL85" t="s" s="2">
         <v>20</v>
@@ -11815,14 +11823,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -11844,13 +11852,13 @@
         <v>130</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11900,7 +11908,7 @@
         <v>20</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>81</v>
@@ -11915,7 +11923,7 @@
         <v>136</v>
       </c>
       <c r="AK86" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL86" t="s" s="2">
         <v>20</v>
@@ -11929,14 +11937,14 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E87" s="2"/>
       <c r="F87" t="s" s="2">
@@ -11958,16 +11966,16 @@
         <v>130</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>20</v>
@@ -12016,7 +12024,7 @@
         <v>20</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>81</v>
@@ -12045,10 +12053,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12074,10 +12082,10 @@
         <v>87</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -12128,7 +12136,7 @@
         <v>20</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>77</v>
@@ -12157,10 +12165,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12186,10 +12194,10 @@
         <v>105</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12216,13 +12224,13 @@
         <v>20</v>
       </c>
       <c r="X89" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y89" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="Z89" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="AA89" t="s" s="2">
         <v>20</v>
@@ -12240,7 +12248,7 @@
         <v>20</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>77</v>
@@ -12269,10 +12277,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12295,13 +12303,13 @@
         <v>20</v>
       </c>
       <c r="K90" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" s="2"/>
@@ -12352,7 +12360,7 @@
         <v>20</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>81</v>
@@ -12381,10 +12389,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12407,13 +12415,13 @@
         <v>20</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" s="2"/>
@@ -12464,7 +12472,7 @@
         <v>20</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>81</v>
@@ -12493,10 +12501,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12519,13 +12527,13 @@
         <v>20</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" s="2"/>
@@ -12576,7 +12584,7 @@
         <v>20</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>81</v>
@@ -12605,10 +12613,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12631,13 +12639,13 @@
         <v>20</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" s="2"/>
@@ -12688,7 +12696,7 @@
         <v>20</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>81</v>
@@ -12703,7 +12711,7 @@
         <v>20</v>
       </c>
       <c r="AK93" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL93" t="s" s="2">
         <v>20</v>
@@ -12717,14 +12725,14 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E94" s="2"/>
       <c r="F94" t="s" s="2">
@@ -12746,13 +12754,13 @@
         <v>130</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -12802,7 +12810,7 @@
         <v>20</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>81</v>
@@ -12817,7 +12825,7 @@
         <v>136</v>
       </c>
       <c r="AK94" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL94" t="s" s="2">
         <v>20</v>
@@ -12831,14 +12839,14 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E95" s="2"/>
       <c r="F95" t="s" s="2">
@@ -12860,16 +12868,16 @@
         <v>130</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>20</v>
@@ -12918,7 +12926,7 @@
         <v>20</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>81</v>
@@ -12947,10 +12955,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12976,10 +12984,10 @@
         <v>105</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13006,13 +13014,13 @@
         <v>20</v>
       </c>
       <c r="X96" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y96" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="Z96" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AA96" t="s" s="2">
         <v>20</v>
@@ -13030,7 +13038,7 @@
         <v>20</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>77</v>
@@ -13059,10 +13067,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13085,13 +13093,13 @@
         <v>20</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13118,13 +13126,13 @@
         <v>20</v>
       </c>
       <c r="X97" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="Y97" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="Z97" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AA97" t="s" s="2">
         <v>20</v>
@@ -13142,7 +13150,7 @@
         <v>20</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>81</v>
@@ -13171,10 +13179,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -13197,13 +13205,13 @@
         <v>20</v>
       </c>
       <c r="K98" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="N98" s="2"/>
       <c r="O98" s="2"/>
@@ -13230,13 +13238,13 @@
         <v>20</v>
       </c>
       <c r="X98" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="Y98" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="Z98" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AA98" t="s" s="2">
         <v>20</v>
@@ -13254,7 +13262,7 @@
         <v>20</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>81</v>
@@ -13283,10 +13291,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13312,10 +13320,10 @@
         <v>105</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -13342,13 +13350,13 @@
         <v>20</v>
       </c>
       <c r="X99" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y99" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="Z99" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="AA99" t="s" s="2">
         <v>20</v>
@@ -13366,7 +13374,7 @@
         <v>20</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>81</v>
@@ -13395,10 +13403,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13424,10 +13432,10 @@
         <v>105</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" s="2"/>
@@ -13454,13 +13462,13 @@
         <v>20</v>
       </c>
       <c r="X100" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y100" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="Z100" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AA100" t="s" s="2">
         <v>20</v>
@@ -13478,7 +13486,7 @@
         <v>20</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>81</v>
@@ -13507,10 +13515,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13536,10 +13544,10 @@
         <v>105</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -13566,13 +13574,13 @@
         <v>20</v>
       </c>
       <c r="X101" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y101" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="Z101" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AA101" t="s" s="2">
         <v>20</v>
@@ -13590,7 +13598,7 @@
         <v>20</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>81</v>
@@ -13619,10 +13627,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13648,10 +13656,10 @@
         <v>105</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -13678,13 +13686,13 @@
         <v>20</v>
       </c>
       <c r="X102" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y102" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="Z102" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="AA102" t="s" s="2">
         <v>20</v>
@@ -13702,7 +13710,7 @@
         <v>20</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>81</v>
@@ -13731,10 +13739,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -13760,10 +13768,10 @@
         <v>105</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" s="2"/>
@@ -13790,13 +13798,13 @@
         <v>20</v>
       </c>
       <c r="X103" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="Y103" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="Z103" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="AA103" t="s" s="2">
         <v>20</v>
@@ -13814,7 +13822,7 @@
         <v>20</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>81</v>
@@ -13843,10 +13851,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13869,16 +13877,16 @@
         <v>20</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N104" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O104" s="2"/>
       <c r="P104" t="s" s="2">
@@ -13928,7 +13936,7 @@
         <v>20</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>81</v>
@@ -13946,7 +13954,7 @@
         <v>20</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>20</v>
@@ -13957,10 +13965,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13983,16 +13991,16 @@
         <v>20</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14042,7 +14050,7 @@
         <v>20</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>81</v>
@@ -14071,10 +14079,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14097,16 +14105,16 @@
         <v>20</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="O106" s="2"/>
       <c r="P106" t="s" s="2">
@@ -14156,7 +14164,7 @@
         <v>20</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>81</v>
@@ -14185,10 +14193,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14211,13 +14219,13 @@
         <v>20</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -14268,7 +14276,7 @@
         <v>20</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>81</v>
@@ -14283,7 +14291,7 @@
         <v>20</v>
       </c>
       <c r="AK107" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL107" t="s" s="2">
         <v>20</v>
@@ -14297,14 +14305,14 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E108" s="2"/>
       <c r="F108" t="s" s="2">
@@ -14326,13 +14334,13 @@
         <v>130</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O108" s="2"/>
       <c r="P108" t="s" s="2">
@@ -14382,7 +14390,7 @@
         <v>20</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>81</v>
@@ -14397,7 +14405,7 @@
         <v>136</v>
       </c>
       <c r="AK108" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="AL108" t="s" s="2">
         <v>20</v>
@@ -14411,14 +14419,14 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14440,16 +14448,16 @@
         <v>130</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>20</v>
@@ -14498,7 +14506,7 @@
         <v>20</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>81</v>
@@ -14527,10 +14535,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14553,16 +14561,16 @@
         <v>20</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O110" s="2"/>
       <c r="P110" t="s" s="2">
@@ -14612,7 +14620,7 @@
         <v>20</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>81</v>
@@ -14641,10 +14649,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14667,16 +14675,16 @@
         <v>20</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="O111" s="2"/>
       <c r="P111" t="s" s="2">
@@ -14726,7 +14734,7 @@
         <v>20</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>81</v>
@@ -14755,10 +14763,10 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14784,10 +14792,10 @@
         <v>78</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14838,7 +14846,7 @@
         <v>20</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>81</v>
@@ -14856,7 +14864,7 @@
         <v>20</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>20</v>
@@ -14867,12 +14875,12 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:AN112">
-    <filterColumn colId="6">
+    <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
       </customFilters>
     </filterColumn>
-    <filterColumn colId="26">
+    <filterColumn colId="27">
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
